--- a/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est assis. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi. Papa dit : on reste assis, avec l'adulte. La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis. Papa dit : maintenant on sort. Ils sortent ensemble.</t>
+          <t>Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est assis. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi. On reste assis, avec l'adulte. La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis. Maintenant on sort. Ils sortent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est assis. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi.
+papa|On reste assis, avec l'adulte.
+narrateur|La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis.
+papa|Maintenant on sort. Ils sortent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Félix est dans la voiture. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Félix est resté assis. Papa, l'adulte, était là. La ceinture aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Félix tient la main de papa. Ils sentent les fruits du marché.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|Maintenant on sort. Ils sortent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Félix est dans la voiture. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Félix est resté assis. Papa, l'adulte, était là. La ceinture aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1854,7 @@
           <t>narrateur|Félix tient la main de papa. Ils sentent les fruits du marché.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Félix reste assis dans la voiture</t>
+          <t>Le tracteur à la fenêtre de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut voir le tracteur. Elle reste assise, doudou contre elle. Le tracteur passe à la fenêtre. Ils marchent vers le champ après.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est assis. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi. On reste assis, avec l'adulte. La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis. Maintenant on sort. Ils sortent ensemble.</t>
+          <t>Le gravier craque sous les pneus de la voiture. Ça sent le foin, déjà. Une haie d'orties borde le chemin. Le ciel est tout blanc, chaud. Des mouches tournent près du capot. Tu as senti le foin, Sarah ? Ça pique le nez. Oui. On va à la ferme. Sarah tient son doudou gris. Le doudou sent le savon. Je veux le tracteur. Il est dans le champ. On le verra par la fenêtre. En ce moment, Sarah est sur le siège. Papa attache la ceinture, clic. Le tissu est chaud sur les jambes. Ses pieds touchent le repose pieds. On reste assis, avec l'adulte. Tu restes assise, d'accord ? D'accord. La voiture avance tout doux. Les orties reculent, vertes. Sarah serre le doudou. Il est où ? Regarde par la vitre. Un bruit grave arrive, loin. Un gros tracteur rouge apparaît. Le tracteur ! Sarah se penche vers la vitre. Elle a envie de se lever. Tes fesses restent sur le siège. Sarah replace ses fesses. Le doudou reste sur ses genoux. Le tracteur passe tout près. Les grandes roues lèvent la poussière. Il est grand. Tu le vois, assise. Sarah reste assise. Elle colle le nez à la vitre. Le tracteur s'éloigne dans le champ. Au revoir. Il nous attend à la ferme. Le clignotant fait tic, tic. Sarah chante tout bas. Le doudou a une oreille pliée. Tu lui as plié l'oreille ? Un peu. Un papillon tape la vitre, puis part. La poussière du champ reste au soleil.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi. Papa dit : on reste assis, avec l'adulte. La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis. Papa dit : maintenant on sort. Ils sortent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gravier craque sous les pneus de la voiture. Ça sent le foin, déjà. Une haie d'orties borde le chemin. Le ciel est tout blanc, chaud. Des mouches tournent près du capot. Tu as senti le foin, Sarah ? Ça pique le nez. Oui. On va à la ferme. Sarah tient son doudou gris. Le doudou sent le savon. Je veux le tracteur. Il est dans le champ. On le verra par la fenêtre. En ce moment, Sarah est sur le siège. Papa attache la ceinture, clic. Le tissu est chaud sur les jambes. Ses pieds touchent le repose pieds. On reste assis, avec l'adulte. Tu restes assise, d'accord ? D'accord. La voiture avance tout doux. Les orties reculent, vertes. Sarah serre le doudou. Il est où ? Regarde par la vitre. Un bruit grave arrive, loin. Un gros tracteur rouge apparaît. Le tracteur ! Sarah se penche vers la vitre. Elle a envie de se lever. Tes fesses restent sur le siège. Sarah replace ses fesses. Le doudou reste sur ses genoux. Le tracteur passe tout près. Les grandes roues lèvent la poussière. Il est grand. Tu le vois, assise. Sarah reste assise. Elle colle le nez à la vitre. Le tracteur s'éloigne dans le champ. Au revoir. Il nous attend à la ferme. Le clignotant fait tic, tic. Sarah chante tout bas. Le doudou a une oreille pliée. Tu lui as plié l'oreille ? Un peu. Un papillon tape la vitre, puis part. La poussière du champ reste au soleil.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Félix va au marché avec papa. Papa montre le siège. Félix pose ses fesses. Il est assis. Papa attache la ceinture. Les pieds de Félix sont sur le repose-pieds. Papa, c'est l'adulte. Papa s'assoit aussi.
+          <t>narrateur|Le gravier craque sous les pneus de la voiture.
+narrateur|Ça sent le foin, déjà.
+narrateur|Une haie d'orties borde le chemin.
+narrateur|Le ciel est tout blanc, chaud.
+narrateur|Des mouches tournent près du capot.
+papa|Tu as senti le foin, Sarah ?
+enfant-f|Ça pique le nez.
+papa|Oui.
+papa|On va à la ferme.
+narrateur|Sarah tient son doudou gris.
+narrateur|Le doudou sent le savon.
+enfant-f|Je veux le tracteur.
+papa|Il est dans le champ.
+papa|On le verra par la fenêtre.
+narrateur|En ce moment, Sarah est sur le siège.
+narrateur|Papa attache la ceinture, clic.
+narrateur|Le tissu est chaud sur les jambes.
+narrateur|Ses pieds touchent le repose pieds.
 papa|On reste assis, avec l'adulte.
-narrateur|La voiture avance. Félix tient son livre. Il reste assis. Il entend le clignotant. Tic, tic. Félix chante tout bas. Il reste assis, avec papa. La voiture s'arrête. Félix reste assis.
-papa|Maintenant on sort. Ils sortent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu restes assise, d'accord ?
+enfant-f|D'accord.
+narrateur|La voiture avance tout doux.
+narrateur|Les orties reculent, vertes.
+narrateur|Sarah serre le doudou.
+enfant-f|Il est où ?
+papa|Regarde par la vitre.
+narrateur|Un bruit grave arrive, loin.
+narrateur|Un gros tracteur rouge apparaît.
+enfant-f|Le tracteur !
+narrateur|Sarah se penche vers la vitre.
+narrateur|Elle a envie de se lever.
+papa|Tes fesses restent sur le siège.
+narrateur|Sarah replace ses fesses.
+narrateur|Le doudou reste sur ses genoux.
+narrateur|Le tracteur passe tout près.
+narrateur|Les grandes roues lèvent la poussière.
+enfant-f|Il est grand.
+papa|Tu le vois, assise.
+narrateur|Sarah reste assise.
+narrateur|Elle colle le nez à la vitre.
+narrateur|Le tracteur s'éloigne dans le champ.
+enfant-f|Au revoir.
+papa|Il nous attend à la ferme.
+narrateur|Le clignotant fait tic, tic.
+narrateur|Sarah chante tout bas.
+narrateur|Le doudou a une oreille pliée.
+papa|Tu lui as plié l'oreille ?
+enfant-f|Un peu.
+narrateur|Un papillon tape la vitre, puis part.
+narrateur|La poussière du champ reste au soleil.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>voiture</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Félix est dans la voiture. Que fait-il ?</t>
+          <t>Sarah est dans la voiture. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Félix est dans la voiture. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est dans la voiture. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1425,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>assis | rester assis | avec papa | avec l'adulte</t>
+          <t>assis | assise | rester assise | elle reste assise | avec papa | avec l'adulte</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ses fesses sont sur le siège. Avec qui ?</t>
+          <t>Ses fesses sont sur le siège. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1489,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1565,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Félix est dans la voiture. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah est dans la voiture.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Félix est resté assis. Papa, l'adulte, était là. La ceinture aussi.</t>
+          <t>Sarah est restée assise. Le doudou était sur ses genoux. Tes fesses étaient sur le siège. Merci, Sarah. J'ai vu le tracteur. Oui, depuis ta place. La voiture ralentit près d'une barrière. Le bois de la barrière est sec. On arrive ? Oui. On sort quand je le dis. Sarah serre le doudou. Elle reste assise. Une poule traverse le chemin, lente. Une poule. Tu la regardes, assise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Félix est resté &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Papa, l'adulte, était là. La ceinture aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est restée assise. Le doudou était sur ses genoux. Tes fesses étaient sur le siège. Merci, Sarah. J'ai vu le tracteur. Oui, depuis ta place. La voiture ralentit près d'une barrière. Le bois de la barrière est sec. On arrive ? Oui. On sort quand je le dis. Sarah serre le doudou. Elle reste assise. Une poule traverse le chemin, lente. Une poule. Tu la regardes, assise.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1592,14 +1654,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1741,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Félix est resté assis. Papa, l'adulte, était là. La ceinture aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah est restée assise.
+narrateur|Le doudou était sur ses genoux.
+papa|Tes fesses étaient sur le siège.
+papa|Merci, Sarah.
+enfant-f|J'ai vu le tracteur.
+papa|Oui, depuis ta place.
+narrateur|La voiture ralentit près d'une barrière.
+narrateur|Le bois de la barrière est sec.
+enfant-f|On arrive ?
+papa|Oui.
+papa|On sort quand je le dis.
+narrateur|Sarah serre le doudou.
+narrateur|Elle reste assise.
+narrateur|Une poule traverse le chemin, lente.
+enfant-f|Une poule.
+papa|Tu la regardes, assise.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Félix tient la main de papa. Ils sentent les fruits du marché.</t>
+          <t>La voiture s'arrête. Le gravier fait un dernier bruit. Maintenant on sort. Tu me donnes la main ? Oui, papa. Papa défait la ceinture. Sarah descend, doudou contre elle. L'air sent le foin, fort. Le tracteur est là. On y va ensemble. Ils marchent vers le champ. Les grandes roues sont immobiles. Tu l'as d'abord vu, assise. Avec mon doudou. Une mouche tourne près d'une roue. Tu lui donnes l'autre oreille ? Voilà.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Félix tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils sentent les fruits du marché.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La voiture s'arrête. Le gravier fait un dernier bruit. Maintenant on sort. Tu me donnes la main ? Oui, papa. Papa défait la ceinture. Sarah descend, doudou contre elle. L'air sent le foin, fort. Le tracteur est là. On y va ensemble. Ils marchent vers le champ. Les grandes roues sont immobiles. Tu l'as d'abord vu, assise. Avec mon doudou. Une mouche tourne près d'une roue. Tu lui donnes l'autre oreille ? Voilà.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,14 +1844,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1851,10 +1927,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Félix tient la main de papa. Ils sentent les fruits du marché.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La voiture s'arrête.
+narrateur|Le gravier fait un dernier bruit.
+papa|Maintenant on sort.
+papa|Tu me donnes la main ?
+enfant-f|Oui, papa.
+narrateur|Papa défait la ceinture.
+narrateur|Sarah descend, doudou contre elle.
+narrateur|L'air sent le foin, fort.
+enfant-f|Le tracteur est là.
+papa|On y va ensemble.
+narrateur|Ils marchent vers le champ.
+narrateur|Les grandes roues sont immobiles.
+papa|Tu l'as d'abord vu, assise.
+enfant-f|Avec mon doudou.
+narrateur|Une mouche tourne près d'une roue.
+papa|Tu lui donnes l'autre oreille ?
+enfant-f|Voilà.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,12 +1970,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Sarah pose la main sur une roue. Le caoutchouc est chaud et poussiéreux. Il est chaud. Oui. Comme le chemin. Le doudou a de la poussière à l'oreille. Le foin sent encore, tout près.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose la main sur une roue. Le caoutchouc est chaud et poussiéreux. Il est chaud. Oui. Comme le chemin. Le doudou a de la poussière à l'oreille. Le foin sent encore, tout près.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1940,14 +2031,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2019,10 +2110,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Sarah pose la main sur une roue.
+narrateur|Le caoutchouc est chaud et poussiéreux.
+enfant-f|Il est chaud.
+papa|Oui.
+papa|Comme le chemin.
+narrateur|Le doudou a de la poussière à l'oreille.
+narrateur|Le foin sent encore, tout près.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2175,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.TRA.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>voiture</t>
+          <t>voiture, chemin de ferme</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Félix, papa</t>
+          <t>Sarah, papa</t>
         </is>
       </c>
     </row>
